--- a/Roshan-Industries-Product-Catalogue.xlsx
+++ b/Roshan-Industries-Product-Catalogue.xlsx
@@ -18594,8 +18594,10 @@
       <c r="N6" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -18639,8 +18641,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -18684,8 +18688,10 @@
       <c r="N8" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -18729,8 +18735,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -18774,8 +18782,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -18819,8 +18829,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -18864,8 +18876,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -18909,8 +18923,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -18954,8 +18970,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -18999,8 +19017,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -19044,8 +19064,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -19089,8 +19111,10 @@
       <c r="N17" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -19134,8 +19158,10 @@
       <c r="N18" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -19179,8 +19205,10 @@
       <c r="N19" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -19224,8 +19252,10 @@
       <c r="N20" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -19269,8 +19299,10 @@
       <c r="N21" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -19314,8 +19346,10 @@
       <c r="N22" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -19589,8 +19623,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -19634,8 +19670,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -19679,8 +19717,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -19724,8 +19764,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -19769,8 +19811,10 @@
       <c r="N10" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -19814,8 +19858,10 @@
       <c r="N11" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -19859,8 +19905,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -19904,8 +19952,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -19949,8 +19999,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20192,8 +20244,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -20237,8 +20291,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -20282,8 +20338,10 @@
       <c r="N8" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -20327,8 +20385,10 @@
       <c r="N9" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -20372,8 +20432,10 @@
       <c r="N10" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -20417,8 +20479,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -20462,8 +20526,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -20507,8 +20573,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -20552,8 +20620,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -20563,8 +20633,10 @@
       <c r="B15" s="7" t="str">
         <v>Third Hand Base</v>
       </c>
-      <c r="C15" s="7" t="str">
-        <v>Third Hand Base. An additional workpiece support for positioning small items during jewellery bench tasks. Check the pictured joints, clamps and base arrangement with Roshan Industries before selecting the listed version.</v>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third Hand Base. A separate base for a compatible third hand support. The photograph shows the base alone, without an articulated arm or clamp. Confirm the mounting arrangement and compatibility with your existing third hand through Roshan Industries before ordering.</t>
+        </is>
       </c>
       <c r="D15" s="7" t="str">
         <v>Soldering and Helping Hands</v>
@@ -20597,8 +20669,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -20642,8 +20716,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -20687,8 +20763,10 @@
       <c r="N17" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20942,8 +21020,10 @@
       <c r="N6" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -20987,8 +21067,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -21032,8 +21114,10 @@
       <c r="N8" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -21077,8 +21161,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -21122,8 +21208,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -21167,8 +21255,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -21212,8 +21302,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -21257,8 +21349,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21496,8 +21590,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -21541,8 +21637,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -21586,8 +21684,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -21631,8 +21731,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -21676,8 +21778,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -21721,8 +21825,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -21766,8 +21872,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -21811,8 +21919,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -21856,8 +21966,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -21901,8 +22013,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -21946,8 +22060,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -21991,8 +22107,10 @@
       <c r="N17" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -22036,8 +22154,10 @@
       <c r="N18" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -22081,8 +22201,10 @@
       <c r="N19" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -22126,8 +22248,10 @@
       <c r="N20" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -22171,8 +22295,10 @@
       <c r="N21" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -22182,8 +22308,10 @@
       <c r="B22" s="12" t="str">
         <v>Blue Aluminium Base</v>
       </c>
-      <c r="C22" s="12" t="str">
-        <v>Blue Aluminium Base. A bench holder or stand for supporting parts and organising tools during workshop tasks. Confirm the listed configuration and fit for your equipment with Roshan Industries.</v>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blue Aluminium Base. A blue aluminium bench base with drilled positions for arranging small tool attachments. The photograph shows a compact rectangular base with attachments standing upright. Confirm the required hole layout, tool fit and supply configuration with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D22" s="12" t="str">
         <v>Holders and Stands</v>
@@ -22216,8 +22344,10 @@
       <c r="N22" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1">
@@ -22261,8 +22391,10 @@
       <c r="N23" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O23" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1">
@@ -22306,8 +22438,10 @@
       <c r="N24" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1">
@@ -22351,8 +22485,10 @@
       <c r="N25" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O25" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1">
@@ -22394,8 +22530,10 @@
       <c r="N26" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O26" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1">
@@ -22437,8 +22575,10 @@
       <c r="N27" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="O27" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="88" customHeight="1">
@@ -22480,8 +22620,10 @@
       <c r="N28" s="12" t="n">
         <v>1500</v>
       </c>
-      <c r="O28" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="88" customHeight="1">
@@ -22523,8 +22665,10 @@
       <c r="N29" s="7" t="n">
         <v>758</v>
       </c>
-      <c r="O29" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="88" customHeight="1">
@@ -22566,8 +22710,10 @@
       <c r="N30" s="12" t="n">
         <v>583</v>
       </c>
-      <c r="O30" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="88" customHeight="1">
@@ -22609,8 +22755,10 @@
       <c r="N31" s="7" t="n">
         <v>582</v>
       </c>
-      <c r="O31" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="88" customHeight="1">
@@ -22652,8 +22800,10 @@
       <c r="N32" s="12" t="n">
         <v>1280</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="88" customHeight="1">
@@ -22695,8 +22845,10 @@
       <c r="N33" s="7" t="n">
         <v>1280</v>
       </c>
-      <c r="O33" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="88" customHeight="1">
@@ -22738,8 +22890,10 @@
       <c r="N34" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="O34" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="88" customHeight="1">
@@ -22781,8 +22935,10 @@
       <c r="N35" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="O35" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -23108,8 +23264,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -23153,8 +23311,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -23198,8 +23358,10 @@
       <c r="N8" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -23243,8 +23405,10 @@
       <c r="N9" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -23288,8 +23452,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -23333,8 +23499,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -23378,8 +23546,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -23423,8 +23593,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -23468,8 +23640,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -23513,8 +23687,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -23558,8 +23734,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -23603,8 +23781,10 @@
       <c r="N17" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -23648,8 +23828,10 @@
       <c r="N18" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -23693,8 +23875,10 @@
       <c r="N19" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -23738,8 +23922,10 @@
       <c r="N20" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -23783,8 +23969,10 @@
       <c r="N21" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -23828,8 +24016,10 @@
       <c r="N22" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -24103,8 +24293,10 @@
       <c r="N6" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -24148,8 +24340,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -24193,8 +24387,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -24238,8 +24434,10 @@
       <c r="N9" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -24283,8 +24481,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -24328,8 +24528,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -24373,8 +24575,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -24608,8 +24812,10 @@
       <c r="N6" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -24653,8 +24859,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -24698,8 +24906,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -24743,8 +24953,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -24966,8 +25178,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -25009,8 +25223,10 @@
       <c r="N7" s="7" t="n">
         <v>657</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -25052,8 +25268,10 @@
       <c r="N8" s="12" t="n">
         <v>1269</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -25095,8 +25313,10 @@
       <c r="N9" s="7" t="n">
         <v>900</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -25138,8 +25358,10 @@
       <c r="N10" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -25181,8 +25403,10 @@
       <c r="N11" s="7" t="n">
         <v>1457</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -25224,8 +25448,10 @@
       <c r="N12" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -25267,8 +25493,10 @@
       <c r="N13" s="7" t="n">
         <v>1703</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -25310,8 +25538,10 @@
       <c r="N14" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -25353,8 +25583,10 @@
       <c r="N15" s="7" t="n">
         <v>658</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -25396,8 +25628,10 @@
       <c r="N16" s="12" t="n">
         <v>1269</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -25439,8 +25673,10 @@
       <c r="N17" s="7" t="n">
         <v>1494</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -25482,8 +25718,10 @@
       <c r="N18" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -25525,8 +25763,10 @@
       <c r="N19" s="7" t="n">
         <v>1665</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -25568,8 +25808,10 @@
       <c r="N20" s="12" t="n">
         <v>1055</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -25611,8 +25853,10 @@
       <c r="N21" s="7" t="n">
         <v>1254</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -25654,8 +25898,10 @@
       <c r="N22" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1">
@@ -25697,8 +25943,10 @@
       <c r="N23" s="7" t="n">
         <v>676</v>
       </c>
-      <c r="O23" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1">
@@ -25740,8 +25988,10 @@
       <c r="N24" s="12" t="n">
         <v>930</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1">
@@ -25783,8 +26033,10 @@
       <c r="N25" s="7" t="n">
         <v>931</v>
       </c>
-      <c r="O25" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1">
@@ -25826,8 +26078,10 @@
       <c r="N26" s="12" t="n">
         <v>704</v>
       </c>
-      <c r="O26" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1">
@@ -25869,8 +26123,10 @@
       <c r="N27" s="7" t="n">
         <v>1740</v>
       </c>
-      <c r="O27" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="88" customHeight="1">
@@ -25912,8 +26168,10 @@
       <c r="N28" s="12" t="n">
         <v>495</v>
       </c>
-      <c r="O28" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="88" customHeight="1">
@@ -25955,8 +26213,10 @@
       <c r="N29" s="7" t="n">
         <v>824</v>
       </c>
-      <c r="O29" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="88" customHeight="1">
@@ -25998,8 +26258,10 @@
       <c r="N30" s="12" t="n">
         <v>946</v>
       </c>
-      <c r="O30" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="88" customHeight="1">
@@ -26041,8 +26303,10 @@
       <c r="N31" s="7" t="n">
         <v>919</v>
       </c>
-      <c r="O31" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="88" customHeight="1">
@@ -26084,8 +26348,10 @@
       <c r="N32" s="12" t="n">
         <v>809</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="88" customHeight="1">
@@ -26127,8 +26393,10 @@
       <c r="N33" s="7" t="n">
         <v>646</v>
       </c>
-      <c r="O33" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="88" customHeight="1">
@@ -26170,8 +26438,10 @@
       <c r="N34" s="12" t="n">
         <v>795</v>
       </c>
-      <c r="O34" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="88" customHeight="1">
@@ -26213,8 +26483,10 @@
       <c r="N35" s="7" t="n">
         <v>603</v>
       </c>
-      <c r="O35" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="88" customHeight="1">
@@ -26256,8 +26528,10 @@
       <c r="N36" s="12" t="n">
         <v>674</v>
       </c>
-      <c r="O36" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -26587,8 +26861,10 @@
       <c r="N6" s="12" t="n">
         <v>1456</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -26632,8 +26908,10 @@
       <c r="N7" s="7" t="n">
         <v>1389</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -26677,8 +26955,10 @@
       <c r="N8" s="12" t="n">
         <v>1270</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -26722,8 +27002,10 @@
       <c r="N9" s="7" t="n">
         <v>1123</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -26945,8 +27227,10 @@
       <c r="N6" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -26990,8 +27274,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -27035,8 +27321,10 @@
       <c r="N8" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -27080,8 +27368,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -27125,8 +27415,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -27170,8 +27462,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -27215,8 +27509,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -27260,8 +27556,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -27305,8 +27603,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -27350,8 +27650,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -27395,8 +27697,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -27440,8 +27744,10 @@
       <c r="N17" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -27451,8 +27757,10 @@
       <c r="B18" s="12" t="str">
         <v>Plastic Spectacle Eye Glass Number 1 to 1.5</v>
       </c>
-      <c r="C18" s="12" t="str">
-        <v>Plastic Spectacle Eye Glass Number 1 to 1.5. A magnifier for close visual inspection of watch components and small workshop parts. Select the photographed style for your working setup and confirm the required optical variant with Roshan Industries.</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastic Spectacle Eye Glass Number 1 to 1.5. A spectacle-mounted eye loupe with a black body, ridged grey lens ring and metal spectacle attachment, as shown in the reference photograph. It supports close inspection of small watch parts. Confirm the listed optical variant and attachment fit with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D18" s="12" t="str">
         <v>Eye Loupes and Magnifiers</v>
@@ -27485,8 +27793,10 @@
       <c r="N18" s="12" t="n">
         <v>1600</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -27496,8 +27806,10 @@
       <c r="B19" s="7" t="str">
         <v>Plastic Spectacle Eye Glass Number 2 to 4.5</v>
       </c>
-      <c r="C19" s="7" t="str">
-        <v>Plastic Spectacle Eye Glass Number 2 to 4.5. A magnifier for close visual inspection of watch components and small workshop parts. Select the photographed style for your working setup and confirm the required optical variant with Roshan Industries.</v>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastic Spectacle Eye Glass Number 2 to 4.5. A spectacle-mounted eye loupe with a black body, ridged grey lens ring and metal spectacle attachment, as shown in the reference photograph. It supports close inspection of small watch parts. Confirm the listed optical variant and attachment fit with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D19" s="7" t="str">
         <v>Eye Loupes and Magnifiers</v>
@@ -27530,8 +27842,10 @@
       <c r="N19" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -27575,8 +27889,10 @@
       <c r="N20" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -27620,8 +27936,10 @@
       <c r="N21" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -27665,8 +27983,10 @@
       <c r="N22" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1">
@@ -27710,8 +28030,10 @@
       <c r="N23" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O23" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1">
@@ -27755,8 +28077,10 @@
       <c r="N24" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1">
@@ -27800,8 +28124,10 @@
       <c r="N25" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O25" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1">
@@ -27845,8 +28171,10 @@
       <c r="N26" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O26" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1">
@@ -27890,8 +28218,10 @@
       <c r="N27" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O27" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="88" customHeight="1">
@@ -27935,8 +28265,10 @@
       <c r="N28" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O28" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="88" customHeight="1">
@@ -27980,8 +28312,10 @@
       <c r="N29" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O29" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="88" customHeight="1">
@@ -28025,8 +28359,10 @@
       <c r="N30" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O30" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="88" customHeight="1">
@@ -28070,8 +28406,10 @@
       <c r="N31" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O31" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="88" customHeight="1">
@@ -28115,8 +28453,10 @@
       <c r="N32" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="88" customHeight="1">
@@ -28160,8 +28500,10 @@
       <c r="N33" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O33" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="88" customHeight="1">
@@ -28205,8 +28547,10 @@
       <c r="N34" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O34" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="88" customHeight="1">
@@ -28250,8 +28594,10 @@
       <c r="N35" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O35" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="88" customHeight="1">
@@ -28295,8 +28641,10 @@
       <c r="N36" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O36" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="88" customHeight="1">
@@ -28340,8 +28688,10 @@
       <c r="N37" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O37" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="88" customHeight="1">
@@ -28385,8 +28735,10 @@
       <c r="N38" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O38" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="88" customHeight="1">
@@ -28430,8 +28782,10 @@
       <c r="N39" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O39" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="88" customHeight="1">
@@ -28441,8 +28795,10 @@
       <c r="B40" s="12" t="str">
         <v>Clips for Open Ended Watch Straps</v>
       </c>
-      <c r="C40" s="12" t="str">
-        <v>Clips for Open Ended Watch Straps. A workshop tool for bracelet and strap servicing. Share the fastening arrangement and part dimensions with Roshan Industries to confirm the right configuration for your repair work.</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clips for Open Ended Watch Straps. Clips for securing compatible open ended watch straps. The photograph shows the clip components separately so their fastening shape can be compared with the existing strap. Confirm strap width, fastening arrangement and quantity with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D40" s="12" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -28475,8 +28831,10 @@
       <c r="N40" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O40" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="88" customHeight="1">
@@ -28520,8 +28878,10 @@
       <c r="N41" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O41" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="88" customHeight="1">
@@ -28565,8 +28925,10 @@
       <c r="N42" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O42" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="88" customHeight="1">
@@ -28610,8 +28972,10 @@
       <c r="N43" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O43" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="88" customHeight="1">
@@ -28655,8 +29019,10 @@
       <c r="N44" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O44" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="88" customHeight="1">
@@ -28700,8 +29066,10 @@
       <c r="N45" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O45" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="88" customHeight="1">
@@ -28745,8 +29113,10 @@
       <c r="N46" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O46" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="88" customHeight="1">
@@ -28790,8 +29160,10 @@
       <c r="N47" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O47" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="88" customHeight="1">
@@ -28835,8 +29207,10 @@
       <c r="N48" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O48" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="88" customHeight="1">
@@ -28880,8 +29254,10 @@
       <c r="N49" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O49" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="88" customHeight="1">
@@ -28925,8 +29301,10 @@
       <c r="N50" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O50" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="88" customHeight="1">
@@ -28970,8 +29348,10 @@
       <c r="N51" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O51" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="88" customHeight="1">
@@ -29015,8 +29395,10 @@
       <c r="N52" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O52" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="88" customHeight="1">
@@ -29060,8 +29442,10 @@
       <c r="N53" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O53" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="88" customHeight="1">
@@ -29105,8 +29489,10 @@
       <c r="N54" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O54" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="88" customHeight="1">
@@ -29150,8 +29536,10 @@
       <c r="N55" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O55" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="88" customHeight="1">
@@ -29195,8 +29583,10 @@
       <c r="N56" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O56" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="88" customHeight="1">
@@ -29240,8 +29630,10 @@
       <c r="N57" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O57" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="88" customHeight="1">
@@ -29285,8 +29677,10 @@
       <c r="N58" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O58" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="88" customHeight="1">
@@ -29330,8 +29724,10 @@
       <c r="N59" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O59" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="88" customHeight="1">
@@ -29375,8 +29771,10 @@
       <c r="N60" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O60" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="88" customHeight="1">
@@ -29420,8 +29818,10 @@
       <c r="N61" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O61" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="88" customHeight="1">
@@ -29465,8 +29865,10 @@
       <c r="N62" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O62" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="88" customHeight="1">
@@ -29510,8 +29912,10 @@
       <c r="N63" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O63" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="88" customHeight="1">
@@ -29521,8 +29925,10 @@
       <c r="B64" s="12" t="str">
         <v>Oil Cup and Oil Pin Set of 4</v>
       </c>
-      <c r="C64" s="12" t="str">
-        <v>Oil Cup and Oil Pin Set of 4. An applicator for placing lubricant during watch servicing. Confirm the listed single or set arrangement with Roshan Industries to suit your lubrication routine and workshop requirements.</v>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oil Cup and Oil Pin Set of 4. A set combining four oil cups with four oil pins, shown in matching colours. The cups hold small quantities of lubricant while the pins help apply it during watch servicing. Confirm the required set configuration and quantity with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D64" s="12" t="str">
         <v>Oil Cups and Oil Pins</v>
@@ -29555,8 +29961,10 @@
       <c r="N64" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O64" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="88" customHeight="1">
@@ -29566,8 +29974,10 @@
       <c r="B65" s="7" t="str">
         <v>Single Oil Cup and Oil Pin Set</v>
       </c>
-      <c r="C65" s="7" t="str">
-        <v>Single Oil Cup and Oil Pin Set. An applicator for placing lubricant during watch servicing. Confirm the listed single or set arrangement with Roshan Industries to suit your lubrication routine and workshop requirements.</v>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single Oil Cup and Oil Pin Set. A single oil cup and oil pin supplied together for watch servicing. The photographed cup has a removable cover, and the separate pin provides an applicator for small lubrication tasks. Confirm the required configuration and quantity with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D65" s="7" t="str">
         <v>Oil Cups and Oil Pins</v>
@@ -29600,8 +30010,10 @@
       <c r="N65" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O65" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="88" customHeight="1">
@@ -29645,8 +30057,10 @@
       <c r="N66" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O66" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="88" customHeight="1">
@@ -29690,8 +30104,10 @@
       <c r="N67" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O67" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="68" ht="88" customHeight="1">
@@ -29735,8 +30151,10 @@
       <c r="N68" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O68" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="88" customHeight="1">
@@ -29780,8 +30198,10 @@
       <c r="N69" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O69" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="88" customHeight="1">
@@ -29825,8 +30245,10 @@
       <c r="N70" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O70" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="88" customHeight="1">
@@ -29870,8 +30292,10 @@
       <c r="N71" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O71" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="88" customHeight="1">
@@ -29915,8 +30339,10 @@
       <c r="N72" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O72" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="88" customHeight="1">
@@ -29960,8 +30386,10 @@
       <c r="N73" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O73" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="88" customHeight="1">
@@ -30005,8 +30433,10 @@
       <c r="N74" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O74" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="88" customHeight="1">
@@ -30050,8 +30480,10 @@
       <c r="N75" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O75" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="88" customHeight="1">
@@ -30095,8 +30527,10 @@
       <c r="N76" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O76" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O76" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="88" customHeight="1">
@@ -30140,8 +30574,10 @@
       <c r="N77" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O77" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="88" customHeight="1">
@@ -30185,8 +30621,10 @@
       <c r="N78" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O78" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="88" customHeight="1">
@@ -30230,8 +30668,10 @@
       <c r="N79" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O79" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="88" customHeight="1">
@@ -30275,8 +30715,10 @@
       <c r="N80" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O80" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="88" customHeight="1">
@@ -30320,8 +30762,10 @@
       <c r="N81" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O81" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="88" customHeight="1">
@@ -30365,8 +30809,10 @@
       <c r="N82" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O82" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="88" customHeight="1">
@@ -30410,8 +30856,10 @@
       <c r="N83" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O83" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="88" customHeight="1">
@@ -30455,8 +30903,10 @@
       <c r="N84" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O84" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="88" customHeight="1">
@@ -30466,8 +30916,10 @@
       <c r="B85" s="7" t="str">
         <v>Third Hand Base</v>
       </c>
-      <c r="C85" s="7" t="str">
-        <v>Third Hand Base. An additional workpiece support for positioning small items during jewellery bench tasks. Check the pictured joints, clamps and base arrangement with Roshan Industries before selecting the listed version.</v>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third Hand Base. A separate base for a compatible third hand support. The photograph shows the base alone, without an articulated arm or clamp. Confirm the mounting arrangement and compatibility with your existing third hand through Roshan Industries before ordering.</t>
+        </is>
       </c>
       <c r="D85" s="7" t="str">
         <v>Soldering and Helping Hands</v>
@@ -30500,8 +30952,10 @@
       <c r="N85" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O85" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="88" customHeight="1">
@@ -30545,8 +30999,10 @@
       <c r="N86" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O86" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="88" customHeight="1">
@@ -30590,8 +31046,10 @@
       <c r="N87" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O87" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="88" customHeight="1">
@@ -30635,8 +31093,10 @@
       <c r="N88" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O88" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="88" customHeight="1">
@@ -30680,8 +31140,10 @@
       <c r="N89" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O89" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="88" customHeight="1">
@@ -30725,8 +31187,10 @@
       <c r="N90" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O90" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="88" customHeight="1">
@@ -30770,8 +31234,10 @@
       <c r="N91" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O91" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="88" customHeight="1">
@@ -30815,8 +31281,10 @@
       <c r="N92" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O92" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="88" customHeight="1">
@@ -30860,8 +31328,10 @@
       <c r="N93" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O93" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="88" customHeight="1">
@@ -30905,8 +31375,10 @@
       <c r="N94" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O94" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="88" customHeight="1">
@@ -30950,8 +31422,10 @@
       <c r="N95" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O95" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="88" customHeight="1">
@@ -30995,8 +31469,10 @@
       <c r="N96" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O96" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="88" customHeight="1">
@@ -31040,8 +31516,10 @@
       <c r="N97" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O97" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="98" ht="88" customHeight="1">
@@ -31085,8 +31563,10 @@
       <c r="N98" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O98" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="88" customHeight="1">
@@ -31130,8 +31610,10 @@
       <c r="N99" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O99" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="88" customHeight="1">
@@ -31175,8 +31657,10 @@
       <c r="N100" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O100" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="88" customHeight="1">
@@ -31220,8 +31704,10 @@
       <c r="N101" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O101" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="102" ht="88" customHeight="1">
@@ -31265,8 +31751,10 @@
       <c r="N102" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O102" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="103" ht="88" customHeight="1">
@@ -31310,8 +31798,10 @@
       <c r="N103" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O103" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="88" customHeight="1">
@@ -31355,8 +31845,10 @@
       <c r="N104" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O104" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="88" customHeight="1">
@@ -31400,8 +31892,10 @@
       <c r="N105" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O105" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="106" ht="88" customHeight="1">
@@ -31445,8 +31939,10 @@
       <c r="N106" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O106" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="107" ht="88" customHeight="1">
@@ -31490,8 +31986,10 @@
       <c r="N107" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O107" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="108" ht="88" customHeight="1">
@@ -31535,8 +32033,10 @@
       <c r="N108" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O108" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="109" ht="88" customHeight="1">
@@ -31580,8 +32080,10 @@
       <c r="N109" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O109" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="110" ht="88" customHeight="1">
@@ -31625,8 +32127,10 @@
       <c r="N110" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O110" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="88" customHeight="1">
@@ -31670,8 +32174,10 @@
       <c r="N111" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O111" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="88" customHeight="1">
@@ -31715,8 +32221,10 @@
       <c r="N112" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O112" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O112" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="113" ht="88" customHeight="1">
@@ -31760,8 +32268,10 @@
       <c r="N113" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O113" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="114" ht="88" customHeight="1">
@@ -31805,8 +32315,10 @@
       <c r="N114" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O114" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O114" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="115" ht="88" customHeight="1">
@@ -31850,8 +32362,10 @@
       <c r="N115" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O115" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="116" ht="88" customHeight="1">
@@ -31895,8 +32409,10 @@
       <c r="N116" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O116" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O116" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="117" ht="88" customHeight="1">
@@ -31940,8 +32456,10 @@
       <c r="N117" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O117" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="118" ht="88" customHeight="1">
@@ -31985,8 +32503,10 @@
       <c r="N118" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O118" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="119" ht="88" customHeight="1">
@@ -32030,8 +32550,10 @@
       <c r="N119" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O119" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="120" ht="88" customHeight="1">
@@ -32075,8 +32597,10 @@
       <c r="N120" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O120" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O120" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="121" ht="88" customHeight="1">
@@ -32120,8 +32644,10 @@
       <c r="N121" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O121" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="122" ht="88" customHeight="1">
@@ -32165,8 +32691,10 @@
       <c r="N122" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O122" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="123" ht="88" customHeight="1">
@@ -32210,8 +32738,10 @@
       <c r="N123" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O123" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="124" ht="88" customHeight="1">
@@ -32255,8 +32785,10 @@
       <c r="N124" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O124" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="125" ht="88" customHeight="1">
@@ -32300,8 +32832,10 @@
       <c r="N125" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O125" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="126" ht="88" customHeight="1">
@@ -32345,8 +32879,10 @@
       <c r="N126" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O126" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="127" ht="88" customHeight="1">
@@ -32390,8 +32926,10 @@
       <c r="N127" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O127" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="128" ht="88" customHeight="1">
@@ -32435,8 +32973,10 @@
       <c r="N128" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O128" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O128" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="129" ht="88" customHeight="1">
@@ -32480,8 +33020,10 @@
       <c r="N129" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O129" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="130" ht="88" customHeight="1">
@@ -32525,8 +33067,10 @@
       <c r="N130" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O130" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O130" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="131" ht="88" customHeight="1">
@@ -32570,8 +33114,10 @@
       <c r="N131" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O131" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="132" ht="88" customHeight="1">
@@ -32615,8 +33161,10 @@
       <c r="N132" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O132" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O132" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="133" ht="88" customHeight="1">
@@ -32660,8 +33208,10 @@
       <c r="N133" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O133" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="134" ht="88" customHeight="1">
@@ -32705,8 +33255,10 @@
       <c r="N134" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O134" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O134" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="135" ht="88" customHeight="1">
@@ -32750,8 +33302,10 @@
       <c r="N135" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O135" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="136" ht="88" customHeight="1">
@@ -32795,8 +33349,10 @@
       <c r="N136" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O136" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O136" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="137" ht="88" customHeight="1">
@@ -32840,8 +33396,10 @@
       <c r="N137" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O137" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="138" ht="88" customHeight="1">
@@ -32885,8 +33443,10 @@
       <c r="N138" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O138" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O138" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="139" ht="88" customHeight="1">
@@ -32930,8 +33490,10 @@
       <c r="N139" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O139" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="140" ht="88" customHeight="1">
@@ -32975,8 +33537,10 @@
       <c r="N140" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O140" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O140" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="141" ht="88" customHeight="1">
@@ -33020,8 +33584,10 @@
       <c r="N141" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O141" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="142" ht="88" customHeight="1">
@@ -33065,8 +33631,10 @@
       <c r="N142" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O142" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O142" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="143" ht="88" customHeight="1">
@@ -33110,8 +33678,10 @@
       <c r="N143" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O143" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="144" ht="88" customHeight="1">
@@ -33155,8 +33725,10 @@
       <c r="N144" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O144" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O144" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="145" ht="88" customHeight="1">
@@ -33200,8 +33772,10 @@
       <c r="N145" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O145" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="146" ht="88" customHeight="1">
@@ -33245,8 +33819,10 @@
       <c r="N146" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O146" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O146" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="147" ht="88" customHeight="1">
@@ -33290,8 +33866,10 @@
       <c r="N147" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O147" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O147" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="148" ht="88" customHeight="1">
@@ -33335,8 +33913,10 @@
       <c r="N148" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O148" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O148" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="149" ht="88" customHeight="1">
@@ -33346,8 +33926,10 @@
       <c r="B149" s="7" t="str">
         <v>Aluminium Knife Case Opener Replacement Blade</v>
       </c>
-      <c r="C149" s="7" t="str">
-        <v>Aluminium Knife Case Opener Replacement Blade. A servicing tool for working with watch case backs. Discuss the case construction and opening method with Roshan Industries to confirm compatibility before ordering.</v>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium Knife Case Opener Replacement Blade. A replacement blade for a compatible aluminium knife case opener. The photograph shows the blade on its own, without the opener handle. Compare its fixing hole and blade shape with your existing opener, and confirm compatibility with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D149" s="7" t="str">
         <v>Case Opening Tools</v>
@@ -33380,8 +33962,10 @@
       <c r="N149" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O149" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="150" ht="88" customHeight="1">
@@ -33425,8 +34009,10 @@
       <c r="N150" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O150" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="151" ht="88" customHeight="1">
@@ -33470,8 +34056,10 @@
       <c r="N151" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O151" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O151" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="152" ht="88" customHeight="1">
@@ -33515,8 +34103,10 @@
       <c r="N152" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O152" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O152" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="153" ht="88" customHeight="1">
@@ -33560,8 +34150,10 @@
       <c r="N153" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O153" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="154" ht="88" customHeight="1">
@@ -33605,8 +34197,10 @@
       <c r="N154" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O154" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O154" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="155" ht="88" customHeight="1">
@@ -33650,8 +34244,10 @@
       <c r="N155" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O155" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O155" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="156" ht="88" customHeight="1">
@@ -33695,8 +34291,10 @@
       <c r="N156" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O156" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O156" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="157" ht="88" customHeight="1">
@@ -33740,8 +34338,10 @@
       <c r="N157" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O157" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O157" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="158" ht="88" customHeight="1">
@@ -33785,8 +34385,10 @@
       <c r="N158" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O158" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O158" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="159" ht="88" customHeight="1">
@@ -33830,8 +34432,10 @@
       <c r="N159" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O159" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="160" ht="88" customHeight="1">
@@ -33875,8 +34479,10 @@
       <c r="N160" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O160" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O160" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="161" ht="88" customHeight="1">
@@ -33920,8 +34526,10 @@
       <c r="N161" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O161" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="162" ht="88" customHeight="1">
@@ -33965,8 +34573,10 @@
       <c r="N162" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O162" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O162" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="163" ht="88" customHeight="1">
@@ -34010,8 +34620,10 @@
       <c r="N163" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O163" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="164" ht="88" customHeight="1">
@@ -34055,8 +34667,10 @@
       <c r="N164" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O164" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O164" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="165" ht="88" customHeight="1">
@@ -34100,8 +34714,10 @@
       <c r="N165" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O165" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O165" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="166" ht="88" customHeight="1">
@@ -34145,8 +34761,10 @@
       <c r="N166" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O166" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O166" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="167" ht="88" customHeight="1">
@@ -34190,8 +34808,10 @@
       <c r="N167" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O167" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="168" ht="88" customHeight="1">
@@ -34235,8 +34855,10 @@
       <c r="N168" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O168" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O168" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="169" ht="88" customHeight="1">
@@ -34280,8 +34902,10 @@
       <c r="N169" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O169" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="170" ht="88" customHeight="1">
@@ -34325,8 +34949,10 @@
       <c r="N170" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O170" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O170" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="171" ht="88" customHeight="1">
@@ -34370,8 +34996,10 @@
       <c r="N171" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O171" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="172" ht="88" customHeight="1">
@@ -34415,8 +35043,10 @@
       <c r="N172" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O172" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O172" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="173" ht="88" customHeight="1">
@@ -34460,8 +35090,10 @@
       <c r="N173" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O173" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="174" ht="88" customHeight="1">
@@ -34505,8 +35137,10 @@
       <c r="N174" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O174" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O174" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="175" ht="88" customHeight="1">
@@ -34550,8 +35184,10 @@
       <c r="N175" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O175" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="176" ht="88" customHeight="1">
@@ -34595,8 +35231,10 @@
       <c r="N176" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O176" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O176" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="177" ht="88" customHeight="1">
@@ -34606,8 +35244,10 @@
       <c r="B177" s="7" t="str">
         <v>Screwdriver with Four Replacement Pins</v>
       </c>
-      <c r="C177" s="7" t="str">
-        <v>Screwdriver with Four Replacement Pins. A replacement pin accessory for compatible bracelet link removal tools. Confirm the listed pin size and attachment arrangement with Roshan Industries against your existing equipment.</v>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Screwdriver with Four Replacement Pins. A screwdriver handle supplied with four interchangeable replacement tips, pictured separately below the handle. The removable tips allow the working end to be selected for small screw tasks. Confirm the required tip profiles and fitting with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D177" s="7" t="str">
         <v>Precision Screwdrivers</v>
@@ -34640,8 +35280,10 @@
       <c r="N177" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O177" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="178" ht="88" customHeight="1">
@@ -34685,8 +35327,10 @@
       <c r="N178" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O178" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O178" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="179" ht="88" customHeight="1">
@@ -34730,8 +35374,10 @@
       <c r="N179" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O179" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="180" ht="88" customHeight="1">
@@ -34775,8 +35421,10 @@
       <c r="N180" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O180" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O180" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="181" ht="88" customHeight="1">
@@ -34820,8 +35468,10 @@
       <c r="N181" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O181" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="182" ht="88" customHeight="1">
@@ -34865,8 +35515,10 @@
       <c r="N182" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O182" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O182" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="183" ht="88" customHeight="1">
@@ -34910,8 +35562,10 @@
       <c r="N183" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O183" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O183" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="184" ht="88" customHeight="1">
@@ -34955,8 +35609,10 @@
       <c r="N184" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O184" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O184" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="185" ht="88" customHeight="1">
@@ -35000,8 +35656,10 @@
       <c r="N185" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O185" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O185" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="186" ht="88" customHeight="1">
@@ -35011,8 +35669,10 @@
       <c r="B186" s="12" t="str">
         <v>MS Link Remover Pillar Set</v>
       </c>
-      <c r="C186" s="12" t="str">
-        <v>MS Link Remover Pillar Set. A tool for removing bracelet link pins during watch strap adjustment. Match the pictured operating arrangement and listed accessories to the bracelet, and confirm suitability with Roshan Industries.</v>
+      <c r="C186" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS Link Remover Pillar Set. A pillar and attachment set for a compatible bracelet link removal tool. The photograph shows separate pillars, working attachments and fittings for matching to an existing tool. Confirm the mounting dimensions and required configuration with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D186" s="12" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -35045,8 +35705,10 @@
       <c r="N186" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O186" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O186" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="187" ht="88" customHeight="1">
@@ -35056,8 +35718,10 @@
       <c r="B187" s="7" t="str">
         <v>Stainless Steel Link Remover Pillar Set</v>
       </c>
-      <c r="C187" s="7" t="str">
-        <v>Stainless Steel Link Remover Pillar Set. A tool for removing bracelet link pins during watch strap adjustment. Match the pictured operating arrangement and listed accessories to the bracelet, and confirm suitability with Roshan Industries.</v>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stainless Steel Link Remover Pillar Set. A pillar and attachment set for a compatible bracelet link removal tool. The photograph shows separate pillars, working attachments and fittings for matching to an existing tool. Confirm the mounting dimensions and required configuration with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D187" s="7" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -35090,8 +35754,10 @@
       <c r="N187" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O187" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="188" ht="88" customHeight="1">
@@ -35135,8 +35801,10 @@
       <c r="N188" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O188" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O188" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="189" ht="88" customHeight="1">
@@ -35180,8 +35848,10 @@
       <c r="N189" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O189" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O189" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="190" ht="88" customHeight="1">
@@ -35191,8 +35861,10 @@
       <c r="B190" s="12" t="str">
         <v>Blue Aluminium Base</v>
       </c>
-      <c r="C190" s="12" t="str">
-        <v>Blue Aluminium Base. A bench holder or stand for supporting parts and organising tools during workshop tasks. Confirm the listed configuration and fit for your equipment with Roshan Industries.</v>
+      <c r="C190" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blue Aluminium Base. A blue aluminium bench base with drilled positions for arranging small tool attachments. The photograph shows a compact rectangular base with attachments standing upright. Confirm the required hole layout, tool fit and supply configuration with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D190" s="12" t="str">
         <v>Holders and Stands</v>
@@ -35225,8 +35897,10 @@
       <c r="N190" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O190" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O190" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="191" ht="88" customHeight="1">
@@ -35236,8 +35910,10 @@
       <c r="B191" s="7" t="str">
         <v>Watch Strap Holder</v>
       </c>
-      <c r="C191" s="7" t="str">
-        <v>Watch Strap Holder. A workshop tool for bracelet and strap servicing. Share the fastening arrangement and part dimensions with Roshan Industries to confirm the right configuration for your repair work.</v>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Watch Strap Holder. A bench holder for positioning a watch strap during servicing. The photograph shows a flat blue base with two upright bent supports and a central round support. Confirm strap dimensions and the required working arrangement with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D191" s="7" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -35270,8 +35946,10 @@
       <c r="N191" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O191" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O191" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="192" ht="88" customHeight="1">
@@ -35315,8 +35993,10 @@
       <c r="N192" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O192" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O192" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="193" ht="88" customHeight="1">
@@ -35360,8 +36040,10 @@
       <c r="N193" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O193" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O193" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="194" ht="88" customHeight="1">
@@ -35405,8 +36087,10 @@
       <c r="N194" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O194" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O194" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="195" ht="88" customHeight="1">
@@ -35450,8 +36134,10 @@
       <c r="N195" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O195" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="196" ht="88" customHeight="1">
@@ -35495,8 +36181,10 @@
       <c r="N196" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O196" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O196" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="197" ht="88" customHeight="1">
@@ -35540,8 +36228,10 @@
       <c r="N197" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O197" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O197" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="198" ht="88" customHeight="1">
@@ -35585,8 +36275,10 @@
       <c r="N198" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O198" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O198" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="199" ht="88" customHeight="1">
@@ -35630,8 +36322,10 @@
       <c r="N199" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O199" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O199" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="200" ht="88" customHeight="1">
@@ -35675,8 +36369,10 @@
       <c r="N200" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O200" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O200" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="201" ht="88" customHeight="1">
@@ -35686,8 +36382,10 @@
       <c r="B201" s="7" t="str">
         <v>Round and Square Delrin Fitting Bases</v>
       </c>
-      <c r="C201" s="7" t="str">
-        <v>Round and Square Delrin Fitting Bases. A fitting machine or base for controlled watch glass assembly and servicing. Confirm the listed model and base compatibility with Roshan Industries against your watch and workshop equipment.</v>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round and Square Delrin Fitting Bases. Separate round and square fitting bases for a compatible watch glass fitting press. The photograph shows the bases and attachments without a press frame. Confirm the required sizes, mounting arrangement and press compatibility with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D201" s="7" t="str">
         <v>Glass and Hand Fitting</v>
@@ -35720,8 +36418,10 @@
       <c r="N201" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O201" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O201" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="202" ht="88" customHeight="1">
@@ -35765,8 +36465,10 @@
       <c r="N202" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O202" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O202" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="203" ht="88" customHeight="1">
@@ -35776,8 +36478,10 @@
       <c r="B203" s="7" t="str">
         <v>Square Delrin Base Set of 6</v>
       </c>
-      <c r="C203" s="7" t="str">
-        <v>Square Delrin Base Set of 6. A fitting machine or base for controlled watch glass assembly and servicing. Confirm the listed model and base compatibility with Roshan Industries against your watch and workshop equipment.</v>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Square Delrin Base Set of 6. A set of six square fitting bases for a compatible watch glass fitting press. The photograph shows individual bases with central mounting points. Confirm the required base sizes, attachment arrangement and press compatibility with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D203" s="7" t="str">
         <v>Glass and Hand Fitting</v>
@@ -35810,8 +36514,10 @@
       <c r="N203" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O203" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="204" ht="88" customHeight="1">
@@ -35855,8 +36561,10 @@
       <c r="N204" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O204" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O204" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="205" ht="88" customHeight="1">
@@ -35900,8 +36608,10 @@
       <c r="N205" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O205" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O205" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="206" ht="88" customHeight="1">
@@ -35945,8 +36655,10 @@
       <c r="N206" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O206" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O206" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="207" ht="88" customHeight="1">
@@ -35990,8 +36702,10 @@
       <c r="N207" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O207" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O207" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="208" ht="88" customHeight="1">
@@ -36035,8 +36749,10 @@
       <c r="N208" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O208" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O208" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="209" ht="88" customHeight="1">
@@ -36080,8 +36796,10 @@
       <c r="N209" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O209" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O209" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="210" ht="88" customHeight="1">
@@ -36125,8 +36843,10 @@
       <c r="N210" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O210" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O210" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="211" ht="88" customHeight="1">
@@ -36170,8 +36890,10 @@
       <c r="N211" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O211" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O211" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="212" ht="88" customHeight="1">
@@ -36215,8 +36937,10 @@
       <c r="N212" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O212" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O212" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="213" ht="88" customHeight="1">
@@ -36260,8 +36984,10 @@
       <c r="N213" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O213" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O213" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="214" ht="88" customHeight="1">
@@ -36305,8 +37031,10 @@
       <c r="N214" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O214" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O214" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="215" ht="88" customHeight="1">
@@ -36350,8 +37078,10 @@
       <c r="N215" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O215" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O215" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="216" ht="88" customHeight="1">
@@ -36395,8 +37125,10 @@
       <c r="N216" s="12" t="n">
         <v>1175</v>
       </c>
-      <c r="O216" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O216" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="217" ht="88" customHeight="1">
@@ -36440,8 +37172,10 @@
       <c r="N217" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O217" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O217" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="218" ht="88" customHeight="1">
@@ -36485,8 +37219,10 @@
       <c r="N218" s="12" t="n">
         <v>1456</v>
       </c>
-      <c r="O218" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O218" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="219" ht="88" customHeight="1">
@@ -36530,8 +37266,10 @@
       <c r="N219" s="7" t="n">
         <v>1389</v>
       </c>
-      <c r="O219" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O219" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="220" ht="88" customHeight="1">
@@ -36575,8 +37313,10 @@
       <c r="N220" s="12" t="n">
         <v>1270</v>
       </c>
-      <c r="O220" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O220" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="221" ht="88" customHeight="1">
@@ -36620,8 +37360,10 @@
       <c r="N221" s="7" t="n">
         <v>1123</v>
       </c>
-      <c r="O221" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O221" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="222" ht="88" customHeight="1">
@@ -36663,8 +37405,10 @@
       <c r="N222" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O222" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O222" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="223" ht="88" customHeight="1">
@@ -36706,8 +37450,10 @@
       <c r="N223" s="7" t="n">
         <v>657</v>
       </c>
-      <c r="O223" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O223" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="224" ht="88" customHeight="1">
@@ -36749,8 +37495,10 @@
       <c r="N224" s="12" t="n">
         <v>1269</v>
       </c>
-      <c r="O224" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O224" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="225" ht="88" customHeight="1">
@@ -36792,8 +37540,10 @@
       <c r="N225" s="7" t="n">
         <v>900</v>
       </c>
-      <c r="O225" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="226" ht="88" customHeight="1">
@@ -36835,8 +37585,10 @@
       <c r="N226" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O226" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O226" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="227" ht="88" customHeight="1">
@@ -36878,8 +37630,10 @@
       <c r="N227" s="7" t="n">
         <v>1457</v>
       </c>
-      <c r="O227" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O227" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="228" ht="88" customHeight="1">
@@ -36921,8 +37675,10 @@
       <c r="N228" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O228" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O228" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="229" ht="88" customHeight="1">
@@ -36964,8 +37720,10 @@
       <c r="N229" s="7" t="n">
         <v>1703</v>
       </c>
-      <c r="O229" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O229" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="230" ht="88" customHeight="1">
@@ -37007,8 +37765,10 @@
       <c r="N230" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="O230" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O230" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="231" ht="88" customHeight="1">
@@ -37050,8 +37810,10 @@
       <c r="N231" s="7" t="n">
         <v>658</v>
       </c>
-      <c r="O231" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O231" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="232" ht="88" customHeight="1">
@@ -37093,8 +37855,10 @@
       <c r="N232" s="12" t="n">
         <v>1269</v>
       </c>
-      <c r="O232" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O232" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="233" ht="88" customHeight="1">
@@ -37136,8 +37900,10 @@
       <c r="N233" s="7" t="n">
         <v>1494</v>
       </c>
-      <c r="O233" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O233" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="234" ht="88" customHeight="1">
@@ -37179,8 +37945,10 @@
       <c r="N234" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="O234" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O234" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="235" ht="88" customHeight="1">
@@ -37222,8 +37990,10 @@
       <c r="N235" s="7" t="n">
         <v>1665</v>
       </c>
-      <c r="O235" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O235" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="236" ht="88" customHeight="1">
@@ -37265,8 +38035,10 @@
       <c r="N236" s="12" t="n">
         <v>1055</v>
       </c>
-      <c r="O236" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O236" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="237" ht="88" customHeight="1">
@@ -37308,8 +38080,10 @@
       <c r="N237" s="7" t="n">
         <v>1254</v>
       </c>
-      <c r="O237" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O237" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="238" ht="88" customHeight="1">
@@ -37351,8 +38125,10 @@
       <c r="N238" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="O238" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O238" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="239" ht="88" customHeight="1">
@@ -37394,8 +38170,10 @@
       <c r="N239" s="7" t="n">
         <v>676</v>
       </c>
-      <c r="O239" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O239" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="240" ht="88" customHeight="1">
@@ -37437,8 +38215,10 @@
       <c r="N240" s="12" t="n">
         <v>930</v>
       </c>
-      <c r="O240" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O240" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="241" ht="88" customHeight="1">
@@ -37480,8 +38260,10 @@
       <c r="N241" s="7" t="n">
         <v>931</v>
       </c>
-      <c r="O241" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O241" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="242" ht="88" customHeight="1">
@@ -37523,8 +38305,10 @@
       <c r="N242" s="12" t="n">
         <v>704</v>
       </c>
-      <c r="O242" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O242" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="243" ht="88" customHeight="1">
@@ -37566,8 +38350,10 @@
       <c r="N243" s="7" t="n">
         <v>1740</v>
       </c>
-      <c r="O243" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O243" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="244" ht="88" customHeight="1">
@@ -37609,8 +38395,10 @@
       <c r="N244" s="12" t="n">
         <v>495</v>
       </c>
-      <c r="O244" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O244" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="245" ht="88" customHeight="1">
@@ -37652,8 +38440,10 @@
       <c r="N245" s="7" t="n">
         <v>824</v>
       </c>
-      <c r="O245" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O245" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="246" ht="88" customHeight="1">
@@ -37695,8 +38485,10 @@
       <c r="N246" s="12" t="n">
         <v>946</v>
       </c>
-      <c r="O246" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O246" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="247" ht="88" customHeight="1">
@@ -37738,8 +38530,10 @@
       <c r="N247" s="7" t="n">
         <v>919</v>
       </c>
-      <c r="O247" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O247" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="248" ht="88" customHeight="1">
@@ -37781,8 +38575,10 @@
       <c r="N248" s="12" t="n">
         <v>809</v>
       </c>
-      <c r="O248" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O248" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="249" ht="88" customHeight="1">
@@ -37824,8 +38620,10 @@
       <c r="N249" s="7" t="n">
         <v>646</v>
       </c>
-      <c r="O249" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O249" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="250" ht="88" customHeight="1">
@@ -37867,8 +38665,10 @@
       <c r="N250" s="12" t="n">
         <v>795</v>
       </c>
-      <c r="O250" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O250" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="251" ht="88" customHeight="1">
@@ -37910,8 +38710,10 @@
       <c r="N251" s="7" t="n">
         <v>603</v>
       </c>
-      <c r="O251" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O251" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="252" ht="88" customHeight="1">
@@ -37953,8 +38755,10 @@
       <c r="N252" s="12" t="n">
         <v>674</v>
       </c>
-      <c r="O252" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O252" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="253" ht="88" customHeight="1">
@@ -37996,8 +38800,10 @@
       <c r="N253" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="O253" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O253" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="254" ht="88" customHeight="1">
@@ -38039,8 +38845,10 @@
       <c r="N254" s="12" t="n">
         <v>1500</v>
       </c>
-      <c r="O254" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O254" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="255" ht="88" customHeight="1">
@@ -38082,8 +38890,10 @@
       <c r="N255" s="7" t="n">
         <v>758</v>
       </c>
-      <c r="O255" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O255" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="256" ht="88" customHeight="1">
@@ -38125,8 +38935,10 @@
       <c r="N256" s="12" t="n">
         <v>583</v>
       </c>
-      <c r="O256" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O256" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="257" ht="88" customHeight="1">
@@ -38168,8 +38980,10 @@
       <c r="N257" s="7" t="n">
         <v>582</v>
       </c>
-      <c r="O257" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O257" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="258" ht="88" customHeight="1">
@@ -38211,8 +39025,10 @@
       <c r="N258" s="12" t="n">
         <v>1280</v>
       </c>
-      <c r="O258" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O258" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="259" ht="88" customHeight="1">
@@ -38254,8 +39070,10 @@
       <c r="N259" s="7" t="n">
         <v>1280</v>
       </c>
-      <c r="O259" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O259" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="260" ht="88" customHeight="1">
@@ -38297,8 +39115,10 @@
       <c r="N260" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="O260" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O260" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="261" ht="88" customHeight="1">
@@ -38340,8 +39160,10 @@
       <c r="N261" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="O261" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O261" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="262" ht="88" customHeight="1">
@@ -38383,8 +39205,10 @@
       <c r="N262" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="O262" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O262" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="263" ht="88" customHeight="1">
@@ -38426,8 +39250,10 @@
       <c r="N263" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O263" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O263" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="264" ht="88" customHeight="1">
@@ -38469,8 +39295,10 @@
       <c r="N264" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O264" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O264" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="265" ht="88" customHeight="1">
@@ -38512,8 +39340,10 @@
       <c r="N265" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O265" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O265" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="266" ht="88" customHeight="1">
@@ -38555,8 +39385,10 @@
       <c r="N266" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O266" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O266" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="267" ht="88" customHeight="1">
@@ -38598,8 +39430,10 @@
       <c r="N267" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O267" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O267" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="268" ht="88" customHeight="1">
@@ -38641,8 +39475,10 @@
       <c r="N268" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O268" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O268" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="269" ht="88" customHeight="1">
@@ -38684,8 +39520,10 @@
       <c r="N269" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O269" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O269" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="270" ht="88" customHeight="1">
@@ -38727,8 +39565,10 @@
       <c r="N270" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O270" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O270" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="271" ht="88" customHeight="1">
@@ -38770,8 +39610,10 @@
       <c r="N271" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O271" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O271" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="272" ht="88" customHeight="1">
@@ -38813,8 +39655,10 @@
       <c r="N272" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O272" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O272" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="273" ht="88" customHeight="1">
@@ -38856,8 +39700,10 @@
       <c r="N273" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O273" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O273" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="274" ht="88" customHeight="1">
@@ -38899,8 +39745,10 @@
       <c r="N274" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O274" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O274" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="275" ht="88" customHeight="1">
@@ -38942,8 +39790,10 @@
       <c r="N275" s="7" t="n">
         <v>780</v>
       </c>
-      <c r="O275" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O275" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="276" ht="88" customHeight="1">
@@ -38985,8 +39835,10 @@
       <c r="N276" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O276" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O276" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="277" ht="88" customHeight="1">
@@ -39028,8 +39880,10 @@
       <c r="N277" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O277" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O277" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="278" ht="88" customHeight="1">
@@ -39071,8 +39925,10 @@
       <c r="N278" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O278" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O278" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="279" ht="88" customHeight="1">
@@ -39114,8 +39970,10 @@
       <c r="N279" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O279" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O279" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="280" ht="88" customHeight="1">
@@ -39157,8 +40015,10 @@
       <c r="N280" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O280" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O280" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="281" ht="88" customHeight="1">
@@ -39200,8 +40060,10 @@
       <c r="N281" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O281" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O281" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="282" ht="88" customHeight="1">
@@ -39243,8 +40105,10 @@
       <c r="N282" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O282" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O282" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="283" ht="88" customHeight="1">
@@ -39286,8 +40150,10 @@
       <c r="N283" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O283" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O283" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="284" ht="88" customHeight="1">
@@ -39329,8 +40195,10 @@
       <c r="N284" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O284" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O284" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="285" ht="88" customHeight="1">
@@ -39372,8 +40240,10 @@
       <c r="N285" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O285" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O285" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="286" ht="88" customHeight="1">
@@ -39415,8 +40285,10 @@
       <c r="N286" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O286" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O286" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="287" ht="88" customHeight="1">
@@ -39458,8 +40330,10 @@
       <c r="N287" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O287" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O287" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="288" ht="88" customHeight="1">
@@ -39501,8 +40375,10 @@
       <c r="N288" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O288" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O288" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="289" ht="88" customHeight="1">
@@ -39544,8 +40420,10 @@
       <c r="N289" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O289" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O289" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="290" ht="88" customHeight="1">
@@ -39587,8 +40465,10 @@
       <c r="N290" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O290" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O290" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="291" ht="88" customHeight="1">
@@ -39630,8 +40510,10 @@
       <c r="N291" s="7" t="n">
         <v>889</v>
       </c>
-      <c r="O291" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O291" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="292" ht="88" customHeight="1">
@@ -39673,8 +40555,10 @@
       <c r="N292" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O292" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O292" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="293" ht="88" customHeight="1">
@@ -39716,8 +40600,10 @@
       <c r="N293" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O293" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O293" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="294" ht="88" customHeight="1">
@@ -39759,8 +40645,10 @@
       <c r="N294" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O294" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O294" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="295" ht="88" customHeight="1">
@@ -39802,8 +40690,10 @@
       <c r="N295" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O295" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O295" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="296" ht="88" customHeight="1">
@@ -39845,8 +40735,10 @@
       <c r="N296" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O296" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O296" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="297" ht="88" customHeight="1">
@@ -39888,8 +40780,10 @@
       <c r="N297" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O297" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O297" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="298" ht="88" customHeight="1">
@@ -39931,8 +40825,10 @@
       <c r="N298" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O298" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O298" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="299" ht="88" customHeight="1">
@@ -39974,8 +40870,10 @@
       <c r="N299" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O299" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O299" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="300" ht="88" customHeight="1">
@@ -40017,8 +40915,10 @@
       <c r="N300" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O300" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O300" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="301" ht="88" customHeight="1">
@@ -40060,8 +40960,10 @@
       <c r="N301" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O301" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O301" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="302" ht="88" customHeight="1">
@@ -40103,8 +41005,10 @@
       <c r="N302" s="12" t="n">
         <v>726</v>
       </c>
-      <c r="O302" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O302" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="303" ht="88" customHeight="1">
@@ -40146,8 +41050,10 @@
       <c r="N303" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O303" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O303" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="304" ht="88" customHeight="1">
@@ -40189,8 +41095,10 @@
       <c r="N304" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O304" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O304" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="305" ht="88" customHeight="1">
@@ -40232,8 +41140,10 @@
       <c r="N305" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O305" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O305" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="306" ht="88" customHeight="1">
@@ -40275,8 +41185,10 @@
       <c r="N306" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O306" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O306" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="307" ht="88" customHeight="1">
@@ -40318,8 +41230,10 @@
       <c r="N307" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O307" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O307" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="308" ht="88" customHeight="1">
@@ -40361,8 +41275,10 @@
       <c r="N308" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O308" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O308" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="309" ht="88" customHeight="1">
@@ -40404,8 +41320,10 @@
       <c r="N309" s="7" t="n">
         <v>726</v>
       </c>
-      <c r="O309" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O309" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="310" ht="88" customHeight="1">
@@ -40447,8 +41365,10 @@
       <c r="N310" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O310" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O310" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="311" ht="88" customHeight="1">
@@ -40490,8 +41410,10 @@
       <c r="N311" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O311" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O311" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="312" ht="88" customHeight="1">
@@ -40533,8 +41455,10 @@
       <c r="N312" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O312" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O312" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="313" ht="88" customHeight="1">
@@ -40576,8 +41500,10 @@
       <c r="N313" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O313" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O313" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="314" ht="88" customHeight="1">
@@ -40619,8 +41545,10 @@
       <c r="N314" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O314" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O314" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="315" ht="88" customHeight="1">
@@ -40662,8 +41590,10 @@
       <c r="N315" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O315" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O315" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="316" ht="88" customHeight="1">
@@ -40705,8 +41635,10 @@
       <c r="N316" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O316" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O316" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -42154,8 +43086,10 @@
       <c r="N6" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -42197,8 +43131,10 @@
       <c r="N7" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -42240,8 +43176,10 @@
       <c r="N8" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -42283,8 +43221,10 @@
       <c r="N9" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -42326,8 +43266,10 @@
       <c r="N10" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -42369,8 +43311,10 @@
       <c r="N11" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -42412,8 +43356,10 @@
       <c r="N12" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -42455,8 +43401,10 @@
       <c r="N13" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -42498,8 +43446,10 @@
       <c r="N14" s="12" t="n">
         <v>889</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -42541,8 +43491,10 @@
       <c r="N15" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -42584,8 +43536,10 @@
       <c r="N16" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -42627,8 +43581,10 @@
       <c r="N17" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -42670,8 +43626,10 @@
       <c r="N18" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -42713,8 +43671,10 @@
       <c r="N19" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -42756,8 +43716,10 @@
       <c r="N20" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -42799,8 +43761,10 @@
       <c r="N21" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -42842,8 +43806,10 @@
       <c r="N22" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1">
@@ -42885,8 +43851,10 @@
       <c r="N23" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O23" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1">
@@ -42928,8 +43896,10 @@
       <c r="N24" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1">
@@ -42971,8 +43941,10 @@
       <c r="N25" s="7" t="n">
         <v>726</v>
       </c>
-      <c r="O25" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1">
@@ -43014,8 +43986,10 @@
       <c r="N26" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O26" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1">
@@ -43057,8 +44031,10 @@
       <c r="N27" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O27" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="88" customHeight="1">
@@ -43100,8 +44076,10 @@
       <c r="N28" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O28" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="88" customHeight="1">
@@ -43143,8 +44121,10 @@
       <c r="N29" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O29" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="88" customHeight="1">
@@ -43186,8 +44166,10 @@
       <c r="N30" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O30" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="88" customHeight="1">
@@ -43229,8 +44211,10 @@
       <c r="N31" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O31" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="88" customHeight="1">
@@ -43272,8 +44256,10 @@
       <c r="N32" s="12" t="n">
         <v>726</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="88" customHeight="1">
@@ -43315,8 +44301,10 @@
       <c r="N33" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O33" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -43632,8 +44620,10 @@
       <c r="N6" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -43675,8 +44665,10 @@
       <c r="N7" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -43718,8 +44710,10 @@
       <c r="N8" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -43761,8 +44755,10 @@
       <c r="N9" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -43804,8 +44800,10 @@
       <c r="N10" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -43847,8 +44845,10 @@
       <c r="N11" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -43890,8 +44890,10 @@
       <c r="N12" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -43933,8 +44935,10 @@
       <c r="N13" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -43976,8 +44980,10 @@
       <c r="N14" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -44019,8 +45025,10 @@
       <c r="N15" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -44264,8 +45272,10 @@
       <c r="N6" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -44307,8 +45317,10 @@
       <c r="N7" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -44350,8 +45362,10 @@
       <c r="N8" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -44393,8 +45407,10 @@
       <c r="N9" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -44436,8 +45452,10 @@
       <c r="N10" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -44479,8 +45497,10 @@
       <c r="N11" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -44708,8 +45728,10 @@
       <c r="N6" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -44751,8 +45773,10 @@
       <c r="N7" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -44794,8 +45818,10 @@
       <c r="N8" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -44837,8 +45863,10 @@
       <c r="N9" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -44880,8 +45908,10 @@
       <c r="N10" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -44923,8 +45953,10 @@
       <c r="N11" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -44966,8 +45998,10 @@
       <c r="N12" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -45199,8 +46233,10 @@
       <c r="N6" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -45242,8 +46278,10 @@
       <c r="N7" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -45285,8 +46323,10 @@
       <c r="N8" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -45504,8 +46544,10 @@
       <c r="N6" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -45549,8 +46591,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -45594,8 +46638,10 @@
       <c r="N8" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -45639,8 +46685,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -45684,8 +46732,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -45729,8 +46779,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -45774,8 +46826,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -45819,8 +46873,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -45864,8 +46920,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -45909,8 +46967,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -45954,8 +47014,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -45999,8 +47061,10 @@
       <c r="N17" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -46010,8 +47074,10 @@
       <c r="B18" s="12" t="str">
         <v>Plastic Spectacle Eye Glass Number 1 to 1.5</v>
       </c>
-      <c r="C18" s="12" t="str">
-        <v>Plastic Spectacle Eye Glass Number 1 to 1.5. A magnifier for close visual inspection of watch components and small workshop parts. Select the photographed style for your working setup and confirm the required optical variant with Roshan Industries.</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastic Spectacle Eye Glass Number 1 to 1.5. A spectacle-mounted eye loupe with a black body, ridged grey lens ring and metal spectacle attachment, as shown in the reference photograph. It supports close inspection of small watch parts. Confirm the listed optical variant and attachment fit with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D18" s="12" t="str">
         <v>Eye Loupes and Magnifiers</v>
@@ -46044,8 +47110,10 @@
       <c r="N18" s="12" t="n">
         <v>1600</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -46055,8 +47123,10 @@
       <c r="B19" s="7" t="str">
         <v>Plastic Spectacle Eye Glass Number 2 to 4.5</v>
       </c>
-      <c r="C19" s="7" t="str">
-        <v>Plastic Spectacle Eye Glass Number 2 to 4.5. A magnifier for close visual inspection of watch components and small workshop parts. Select the photographed style for your working setup and confirm the required optical variant with Roshan Industries.</v>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastic Spectacle Eye Glass Number 2 to 4.5. A spectacle-mounted eye loupe with a black body, ridged grey lens ring and metal spectacle attachment, as shown in the reference photograph. It supports close inspection of small watch parts. Confirm the listed optical variant and attachment fit with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D19" s="7" t="str">
         <v>Eye Loupes and Magnifiers</v>
@@ -46089,8 +47159,10 @@
       <c r="N19" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -46134,8 +47206,10 @@
       <c r="N20" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -46179,8 +47253,10 @@
       <c r="N21" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -46224,8 +47300,10 @@
       <c r="N22" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1">
@@ -46269,8 +47347,10 @@
       <c r="N23" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O23" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1">
@@ -46314,8 +47394,10 @@
       <c r="N24" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1">
@@ -46359,8 +47441,10 @@
       <c r="N25" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O25" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1">
@@ -46404,8 +47488,10 @@
       <c r="N26" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O26" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1">
@@ -46449,8 +47535,10 @@
       <c r="N27" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="O27" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -46744,8 +47832,10 @@
       <c r="N6" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -46789,8 +47879,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -46834,8 +47926,10 @@
       <c r="N8" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -46879,8 +47973,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -46924,8 +48020,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -46969,8 +48067,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -47014,8 +48114,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -47059,8 +48161,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -47104,8 +48208,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -47149,8 +48255,10 @@
       <c r="N15" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -47194,8 +48302,10 @@
       <c r="N16" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -47239,8 +48349,10 @@
       <c r="N17" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -47250,8 +48362,10 @@
       <c r="B18" s="12" t="str">
         <v>Screwdriver with Four Replacement Pins</v>
       </c>
-      <c r="C18" s="12" t="str">
-        <v>Screwdriver with Four Replacement Pins. A replacement pin accessory for compatible bracelet link removal tools. Confirm the listed pin size and attachment arrangement with Roshan Industries against your existing equipment.</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Screwdriver with Four Replacement Pins. A screwdriver handle supplied with four interchangeable replacement tips, pictured separately below the handle. The removable tips allow the working end to be selected for small screw tasks. Confirm the required tip profiles and fitting with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D18" s="12" t="str">
         <v>Precision Screwdrivers</v>
@@ -47284,8 +48398,10 @@
       <c r="N18" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -47543,8 +48659,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -47588,8 +48706,10 @@
       <c r="N7" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -47633,8 +48753,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -47644,8 +48766,10 @@
       <c r="B9" s="7" t="str">
         <v>Aluminium Knife Case Opener Replacement Blade</v>
       </c>
-      <c r="C9" s="7" t="str">
-        <v>Aluminium Knife Case Opener Replacement Blade. A servicing tool for working with watch case backs. Discuss the case construction and opening method with Roshan Industries to confirm compatibility before ordering.</v>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium Knife Case Opener Replacement Blade. A replacement blade for a compatible aluminium knife case opener. The photograph shows the blade on its own, without the opener handle. Compare its fixing hole and blade shape with your existing opener, and confirm compatibility with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D9" s="7" t="str">
         <v>Case Opening Tools</v>
@@ -47678,8 +48802,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -47723,8 +48849,10 @@
       <c r="N10" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -47768,8 +48896,10 @@
       <c r="N11" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -47813,8 +48943,10 @@
       <c r="N12" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -47858,8 +48990,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -47903,8 +49037,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -47948,8 +49084,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -47991,8 +49129,10 @@
       <c r="N16" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -48208,8 +49348,10 @@
       <c r="B6" s="12" t="str">
         <v>Clips for Open Ended Watch Straps</v>
       </c>
-      <c r="C6" s="12" t="str">
-        <v>Clips for Open Ended Watch Straps. A workshop tool for bracelet and strap servicing. Share the fastening arrangement and part dimensions with Roshan Industries to confirm the right configuration for your repair work.</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clips for Open Ended Watch Straps. Clips for securing compatible open ended watch straps. The photograph shows the clip components separately so their fastening shape can be compared with the existing strap. Confirm strap width, fastening arrangement and quantity with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D6" s="12" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -48242,8 +49384,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -48287,8 +49431,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -48332,8 +49478,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -48377,8 +49525,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -48422,8 +49572,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -48467,8 +49619,10 @@
       <c r="N11" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -48512,8 +49666,10 @@
       <c r="N12" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -48557,8 +49713,10 @@
       <c r="N13" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -48602,8 +49760,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -48647,8 +49807,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -48692,8 +49854,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -48737,8 +49901,10 @@
       <c r="N17" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -48782,8 +49948,10 @@
       <c r="N18" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -48827,8 +49995,10 @@
       <c r="N19" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -48872,8 +50042,10 @@
       <c r="N20" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -48917,8 +50089,10 @@
       <c r="N21" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -48962,8 +50136,10 @@
       <c r="N22" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1">
@@ -49007,8 +50183,10 @@
       <c r="N23" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O23" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1">
@@ -49052,8 +50230,10 @@
       <c r="N24" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1">
@@ -49097,8 +50277,10 @@
       <c r="N25" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O25" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1">
@@ -49142,8 +50324,10 @@
       <c r="N26" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O26" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1">
@@ -49187,8 +50371,10 @@
       <c r="N27" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O27" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="88" customHeight="1">
@@ -49232,8 +50418,10 @@
       <c r="N28" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O28" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="88" customHeight="1">
@@ -49277,8 +50465,10 @@
       <c r="N29" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O29" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="88" customHeight="1">
@@ -49322,8 +50512,10 @@
       <c r="N30" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O30" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="88" customHeight="1">
@@ -49367,8 +50559,10 @@
       <c r="N31" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O31" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="88" customHeight="1">
@@ -49412,8 +50606,10 @@
       <c r="N32" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="88" customHeight="1">
@@ -49423,8 +50619,10 @@
       <c r="B33" s="7" t="str">
         <v>MS Link Remover Pillar Set</v>
       </c>
-      <c r="C33" s="7" t="str">
-        <v>MS Link Remover Pillar Set. A tool for removing bracelet link pins during watch strap adjustment. Match the pictured operating arrangement and listed accessories to the bracelet, and confirm suitability with Roshan Industries.</v>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS Link Remover Pillar Set. A pillar and attachment set for a compatible bracelet link removal tool. The photograph shows separate pillars, working attachments and fittings for matching to an existing tool. Confirm the mounting dimensions and required configuration with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D33" s="7" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -49457,8 +50655,10 @@
       <c r="N33" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O33" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="88" customHeight="1">
@@ -49468,8 +50668,10 @@
       <c r="B34" s="12" t="str">
         <v>Stainless Steel Link Remover Pillar Set</v>
       </c>
-      <c r="C34" s="12" t="str">
-        <v>Stainless Steel Link Remover Pillar Set. A tool for removing bracelet link pins during watch strap adjustment. Match the pictured operating arrangement and listed accessories to the bracelet, and confirm suitability with Roshan Industries.</v>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stainless Steel Link Remover Pillar Set. A pillar and attachment set for a compatible bracelet link removal tool. The photograph shows separate pillars, working attachments and fittings for matching to an existing tool. Confirm the mounting dimensions and required configuration with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D34" s="12" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -49502,8 +50704,10 @@
       <c r="N34" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O34" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="88" customHeight="1">
@@ -49513,8 +50717,10 @@
       <c r="B35" s="7" t="str">
         <v>Watch Strap Holder</v>
       </c>
-      <c r="C35" s="7" t="str">
-        <v>Watch Strap Holder. A workshop tool for bracelet and strap servicing. Share the fastening arrangement and part dimensions with Roshan Industries to confirm the right configuration for your repair work.</v>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Watch Strap Holder. A bench holder for positioning a watch strap during servicing. The photograph shows a flat blue base with two upright bent supports and a central round support. Confirm strap dimensions and the required working arrangement with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D35" s="7" t="str">
         <v>Bracelet and Strap Tools</v>
@@ -49547,8 +50753,10 @@
       <c r="N35" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O35" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="88" customHeight="1">
@@ -49592,8 +50800,10 @@
       <c r="N36" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O36" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="88" customHeight="1">
@@ -49637,8 +50847,10 @@
       <c r="N37" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O37" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="88" customHeight="1">
@@ -49682,8 +50894,10 @@
       <c r="N38" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O38" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -50021,8 +51235,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -50066,8 +51282,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -50111,8 +51329,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -50156,8 +51376,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -50201,8 +51423,10 @@
       <c r="N10" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -50246,8 +51470,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -50291,8 +51517,10 @@
       <c r="N12" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -50336,8 +51564,10 @@
       <c r="N13" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -50381,8 +51611,10 @@
       <c r="N14" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -50392,8 +51624,10 @@
       <c r="B15" s="7" t="str">
         <v>Round and Square Delrin Fitting Bases</v>
       </c>
-      <c r="C15" s="7" t="str">
-        <v>Round and Square Delrin Fitting Bases. A fitting machine or base for controlled watch glass assembly and servicing. Confirm the listed model and base compatibility with Roshan Industries against your watch and workshop equipment.</v>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round and Square Delrin Fitting Bases. Separate round and square fitting bases for a compatible watch glass fitting press. The photograph shows the bases and attachments without a press frame. Confirm the required sizes, mounting arrangement and press compatibility with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D15" s="7" t="str">
         <v>Glass and Hand Fitting</v>
@@ -50426,8 +51660,10 @@
       <c r="N15" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -50437,8 +51673,10 @@
       <c r="B16" s="12" t="str">
         <v>Square Delrin Base Set of 6</v>
       </c>
-      <c r="C16" s="12" t="str">
-        <v>Square Delrin Base Set of 6. A fitting machine or base for controlled watch glass assembly and servicing. Confirm the listed model and base compatibility with Roshan Industries against your watch and workshop equipment.</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Square Delrin Base Set of 6. A set of six square fitting bases for a compatible watch glass fitting press. The photograph shows individual bases with central mounting points. Confirm the required base sizes, attachment arrangement and press compatibility with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D16" s="12" t="str">
         <v>Glass and Hand Fitting</v>
@@ -50471,8 +51709,10 @@
       <c r="N16" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -50722,8 +51962,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -50767,8 +52009,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -50812,8 +52056,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -50857,8 +52103,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -50868,8 +52116,10 @@
       <c r="B10" s="12" t="str">
         <v>Oil Cup and Oil Pin Set of 4</v>
       </c>
-      <c r="C10" s="12" t="str">
-        <v>Oil Cup and Oil Pin Set of 4. An applicator for placing lubricant during watch servicing. Confirm the listed single or set arrangement with Roshan Industries to suit your lubrication routine and workshop requirements.</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oil Cup and Oil Pin Set of 4. A set combining four oil cups with four oil pins, shown in matching colours. The cups hold small quantities of lubricant while the pins help apply it during watch servicing. Confirm the required set configuration and quantity with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D10" s="12" t="str">
         <v>Oil Cups and Oil Pins</v>
@@ -50902,8 +52152,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -50913,8 +52165,10 @@
       <c r="B11" s="7" t="str">
         <v>Single Oil Cup and Oil Pin Set</v>
       </c>
-      <c r="C11" s="7" t="str">
-        <v>Single Oil Cup and Oil Pin Set. An applicator for placing lubricant during watch servicing. Confirm the listed single or set arrangement with Roshan Industries to suit your lubrication routine and workshop requirements.</v>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single Oil Cup and Oil Pin Set. A single oil cup and oil pin supplied together for watch servicing. The photographed cup has a removable cover, and the separate pin provides an applicator for small lubrication tasks. Confirm the required configuration and quantity with Roshan Industries.</t>
+        </is>
       </c>
       <c r="D11" s="7" t="str">
         <v>Oil Cups and Oil Pins</v>
@@ -50947,8 +52201,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -50992,8 +52248,10 @@
       <c r="N12" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -51037,8 +52295,10 @@
       <c r="N13" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -51082,8 +52342,10 @@
       <c r="N14" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -51325,8 +52587,10 @@
       <c r="N6" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
@@ -51370,8 +52634,10 @@
       <c r="N7" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O7" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
@@ -51415,8 +52681,10 @@
       <c r="N8" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
@@ -51460,8 +52728,10 @@
       <c r="N9" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O9" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -51505,8 +52775,10 @@
       <c r="N10" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
@@ -51550,8 +52822,10 @@
       <c r="N11" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O11" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
@@ -51595,8 +52869,10 @@
       <c r="N12" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
@@ -51640,8 +52916,10 @@
       <c r="N13" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O13" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
@@ -51685,8 +52963,10 @@
       <c r="N14" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
@@ -51730,8 +53010,10 @@
       <c r="N15" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O15" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
@@ -51775,8 +53057,10 @@
       <c r="N16" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
@@ -51820,8 +53104,10 @@
       <c r="N17" s="7" t="n">
         <v>525</v>
       </c>
-      <c r="O17" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
@@ -51865,8 +53151,10 @@
       <c r="N18" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
@@ -51910,8 +53198,10 @@
       <c r="N19" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O19" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1">
@@ -51955,8 +53245,10 @@
       <c r="N20" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1">
@@ -52000,8 +53292,10 @@
       <c r="N21" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O21" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1">
@@ -52045,8 +53339,10 @@
       <c r="N22" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1">
@@ -52090,8 +53386,10 @@
       <c r="N23" s="7" t="n">
         <v>526</v>
       </c>
-      <c r="O23" s="7" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1">
@@ -52135,8 +53433,10 @@
       <c r="N24" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <v>346bc43dcd5eed47b54ebab96be746a28b34aa0aaaf3a6037cdead791e2bf178</v>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c06dfa96b7a4064123d2e27e7c2c2e6f840f4342223d80a97ca2a368e444786</t>
+        </is>
       </c>
     </row>
   </sheetData>
